--- a/hexaly_benchmarking_results/original_2.xlsx
+++ b/hexaly_benchmarking_results/original_2.xlsx
@@ -424,16 +424,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2">
-        <v>-393</v>
+        <v>-359</v>
       </c>
       <c r="C2">
-        <v>-5822</v>
+        <v>-4415</v>
       </c>
       <c r="D2">
-        <v>93.24974235657849</v>
+        <v>91.86862967157417</v>
       </c>
       <c r="E2">
         <v>300</v>
@@ -444,16 +444,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3">
-        <v>-420</v>
+        <v>-393</v>
       </c>
       <c r="C3">
-        <v>-7229</v>
+        <v>-5822</v>
       </c>
       <c r="D3">
-        <v>94.19006778254254</v>
+        <v>93.24974235657849</v>
       </c>
       <c r="E3">
         <v>300</v>
@@ -464,16 +464,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4">
-        <v>-459</v>
+        <v>-420</v>
       </c>
       <c r="C4">
-        <v>-8636</v>
+        <v>-7229</v>
       </c>
       <c r="D4">
-        <v>94.68503937007874</v>
+        <v>94.19006778254254</v>
       </c>
       <c r="E4">
         <v>300</v>
@@ -484,16 +484,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5">
-        <v>-497</v>
+        <v>-459</v>
       </c>
       <c r="C5">
-        <v>-10043</v>
+        <v>-8636</v>
       </c>
       <c r="D5">
-        <v>95.05127949815792</v>
+        <v>94.68503937007874</v>
       </c>
       <c r="E5">
         <v>300</v>
@@ -504,16 +504,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6">
-        <v>-507</v>
+        <v>-497</v>
       </c>
       <c r="C6">
-        <v>-11450</v>
+        <v>-10043</v>
       </c>
       <c r="D6">
-        <v>95.57205240174672</v>
+        <v>95.05127949815792</v>
       </c>
       <c r="E6">
         <v>300</v>
@@ -524,16 +524,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7">
-        <v>-547</v>
+        <v>-507</v>
       </c>
       <c r="C7">
-        <v>-12857</v>
+        <v>-11450</v>
       </c>
       <c r="D7">
-        <v>95.74550828342538</v>
+        <v>95.57205240174672</v>
       </c>
       <c r="E7">
         <v>300</v>
@@ -544,16 +544,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8">
-        <v>-570</v>
+        <v>-547</v>
       </c>
       <c r="C8">
-        <v>-14264</v>
+        <v>-12857</v>
       </c>
       <c r="D8">
-        <v>96.00392596747056</v>
+        <v>95.74550828342538</v>
       </c>
       <c r="E8">
         <v>300</v>
@@ -564,16 +564,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9">
-        <v>-596</v>
+        <v>-570</v>
       </c>
       <c r="C9">
-        <v>-15671</v>
+        <v>-14264</v>
       </c>
       <c r="D9">
-        <v>96.19679663071916</v>
+        <v>96.00392596747056</v>
       </c>
       <c r="E9">
         <v>300</v>
@@ -584,16 +584,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10">
-        <v>-603</v>
+        <v>-596</v>
       </c>
       <c r="C10">
-        <v>-17078</v>
+        <v>-15671</v>
       </c>
       <c r="D10">
-        <v>96.46914158566577</v>
+        <v>96.19679663071916</v>
       </c>
       <c r="E10">
         <v>300</v>
@@ -604,16 +604,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11">
-        <v>-613</v>
+        <v>-603</v>
       </c>
       <c r="C11">
-        <v>-18485</v>
+        <v>-17078</v>
       </c>
       <c r="D11">
-        <v>96.68379767378956</v>
+        <v>96.46914158566577</v>
       </c>
       <c r="E11">
         <v>300</v>
@@ -624,16 +624,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12">
-        <v>-623</v>
+        <v>-613</v>
       </c>
       <c r="C12">
-        <v>-19892</v>
+        <v>-18485</v>
       </c>
       <c r="D12">
-        <v>96.86808767343655</v>
+        <v>96.68379767378956</v>
       </c>
       <c r="E12">
         <v>300</v>
@@ -644,16 +644,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13">
         <v>-623</v>
       </c>
       <c r="C13">
-        <v>-21299</v>
+        <v>-19892</v>
       </c>
       <c r="D13">
-        <v>97.07498004601155</v>
+        <v>96.86808767343655</v>
       </c>
       <c r="E13">
         <v>300</v>
@@ -664,16 +664,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14">
         <v>-623</v>
       </c>
       <c r="C14">
-        <v>-22706</v>
+        <v>-21299</v>
       </c>
       <c r="D14">
-        <v>97.25623183299568</v>
+        <v>97.07498004601155</v>
       </c>
       <c r="E14">
         <v>300</v>
@@ -714,19 +714,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2">
-        <v>-393</v>
+        <v>-359</v>
       </c>
       <c r="C2">
-        <v>-393</v>
+        <v>-359</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>165</v>
+        <v>52</v>
       </c>
       <c r="F2" t="s">
         <v>7</v>
@@ -734,36 +734,36 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>-393</v>
+      </c>
+      <c r="C3">
+        <v>-393</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>188</v>
+      </c>
+      <c r="F3" t="s">
         <v>7</v>
-      </c>
-      <c r="B3">
-        <v>-420</v>
-      </c>
-      <c r="C3">
-        <v>-535</v>
-      </c>
-      <c r="D3">
-        <v>21.49532710280374</v>
-      </c>
-      <c r="E3">
-        <v>300</v>
-      </c>
-      <c r="F3" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4">
-        <v>-454</v>
+        <v>-420</v>
       </c>
       <c r="C4">
-        <v>-623</v>
+        <v>-531</v>
       </c>
       <c r="D4">
-        <v>27.12680577849117</v>
+        <v>20.90395480225989</v>
       </c>
       <c r="E4">
         <v>300</v>
@@ -774,16 +774,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5">
-        <v>-497</v>
+        <v>-454</v>
       </c>
       <c r="C5">
         <v>-623</v>
       </c>
       <c r="D5">
-        <v>20.22471910112359</v>
+        <v>27.12680577849117</v>
       </c>
       <c r="E5">
         <v>300</v>
@@ -794,16 +794,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6">
-        <v>-507</v>
+        <v>-497</v>
       </c>
       <c r="C6">
         <v>-623</v>
       </c>
       <c r="D6">
-        <v>18.61958266452649</v>
+        <v>20.22471910112359</v>
       </c>
       <c r="E6">
         <v>300</v>
@@ -814,16 +814,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7">
-        <v>-546</v>
+        <v>-507</v>
       </c>
       <c r="C7">
         <v>-623</v>
       </c>
       <c r="D7">
-        <v>12.35955056179775</v>
+        <v>18.61958266452649</v>
       </c>
       <c r="E7">
         <v>300</v>
@@ -834,16 +834,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8">
-        <v>-553</v>
+        <v>-546</v>
       </c>
       <c r="C8">
         <v>-623</v>
       </c>
       <c r="D8">
-        <v>11.23595505617977</v>
+        <v>12.35955056179775</v>
       </c>
       <c r="E8">
         <v>300</v>
@@ -854,16 +854,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9">
-        <v>-596</v>
+        <v>-553</v>
       </c>
       <c r="C9">
         <v>-623</v>
       </c>
       <c r="D9">
-        <v>4.333868378812198</v>
+        <v>11.23595505617977</v>
       </c>
       <c r="E9">
         <v>300</v>
@@ -874,16 +874,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10">
-        <v>-603</v>
+        <v>-596</v>
       </c>
       <c r="C10">
         <v>-623</v>
       </c>
       <c r="D10">
-        <v>3.210272873194221</v>
+        <v>4.333868378812198</v>
       </c>
       <c r="E10">
         <v>300</v>
@@ -894,16 +894,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11">
-        <v>-613</v>
+        <v>-603</v>
       </c>
       <c r="C11">
         <v>-623</v>
       </c>
       <c r="D11">
-        <v>1.605136436597111</v>
+        <v>3.210272873194221</v>
       </c>
       <c r="E11">
         <v>300</v>
@@ -914,27 +914,27 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12">
-        <v>-623</v>
+        <v>-613</v>
       </c>
       <c r="C12">
         <v>-623</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>1.605136436597111</v>
       </c>
       <c r="E12">
-        <v>99</v>
+        <v>300</v>
       </c>
       <c r="F12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13">
         <v>-623</v>
@@ -946,7 +946,7 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="F13" t="s">
         <v>7</v>
@@ -954,7 +954,7 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14">
         <v>-623</v>
@@ -966,7 +966,7 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F14" t="s">
         <v>7</v>
@@ -1004,16 +1004,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>-359</v>
       </c>
       <c r="C2">
         <v>-1316</v>
       </c>
       <c r="D2">
-        <v>100</v>
+        <v>72.72036474164135</v>
       </c>
       <c r="E2">
         <v>300</v>
@@ -1024,16 +1024,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>-393</v>
       </c>
       <c r="C3">
         <v>-1316</v>
       </c>
       <c r="D3">
-        <v>100</v>
+        <v>70.13677811550151</v>
       </c>
       <c r="E3">
         <v>300</v>
@@ -1044,16 +1044,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>-420</v>
       </c>
       <c r="C4">
         <v>-1316</v>
       </c>
       <c r="D4">
-        <v>100</v>
+        <v>68.08510638297872</v>
       </c>
       <c r="E4">
         <v>300</v>
@@ -1064,16 +1064,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>-459</v>
       </c>
       <c r="C5">
         <v>-1316</v>
       </c>
       <c r="D5">
-        <v>100</v>
+        <v>65.12158054711246</v>
       </c>
       <c r="E5">
         <v>300</v>
@@ -1084,16 +1084,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>-497</v>
       </c>
       <c r="C6">
         <v>-1316</v>
       </c>
       <c r="D6">
-        <v>100</v>
+        <v>62.23404255319149</v>
       </c>
       <c r="E6">
         <v>300</v>
@@ -1104,16 +1104,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>-507</v>
       </c>
       <c r="C7">
         <v>-1316</v>
       </c>
       <c r="D7">
-        <v>100</v>
+        <v>61.4741641337386</v>
       </c>
       <c r="E7">
         <v>300</v>
@@ -1124,16 +1124,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>-547</v>
       </c>
       <c r="C8">
         <v>-1316</v>
       </c>
       <c r="D8">
-        <v>100</v>
+        <v>58.43465045592705</v>
       </c>
       <c r="E8">
         <v>300</v>
@@ -1144,16 +1144,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>-562</v>
       </c>
       <c r="C9">
         <v>-1316</v>
       </c>
       <c r="D9">
-        <v>100</v>
+        <v>57.29483282674772</v>
       </c>
       <c r="E9">
         <v>300</v>
@@ -1164,16 +1164,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>-596</v>
       </c>
       <c r="C10">
         <v>-1316</v>
       </c>
       <c r="D10">
-        <v>100</v>
+        <v>54.7112462006079</v>
       </c>
       <c r="E10">
         <v>300</v>
@@ -1184,16 +1184,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>-603</v>
       </c>
       <c r="C11">
         <v>-1316</v>
       </c>
       <c r="D11">
-        <v>100</v>
+        <v>54.17933130699089</v>
       </c>
       <c r="E11">
         <v>300</v>
@@ -1204,16 +1204,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>-613</v>
       </c>
       <c r="C12">
         <v>-1316</v>
       </c>
       <c r="D12">
-        <v>100</v>
+        <v>53.419452887538</v>
       </c>
       <c r="E12">
         <v>300</v>
@@ -1224,16 +1224,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>-623</v>
       </c>
       <c r="C13">
         <v>-1316</v>
       </c>
       <c r="D13">
-        <v>100</v>
+        <v>52.6595744680851</v>
       </c>
       <c r="E13">
         <v>300</v>
@@ -1244,16 +1244,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>-623</v>
       </c>
       <c r="C14">
         <v>-1316</v>
       </c>
       <c r="D14">
-        <v>100</v>
+        <v>52.6595744680851</v>
       </c>
       <c r="E14">
         <v>300</v>
@@ -1294,19 +1294,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2">
-        <v>-393</v>
+        <v>-359</v>
       </c>
       <c r="C2">
-        <v>-393</v>
+        <v>-359</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>190</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>7</v>
@@ -1314,19 +1314,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3">
-        <v>-420</v>
+        <v>-393</v>
       </c>
       <c r="C3">
-        <v>-420</v>
+        <v>-393</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="F3" t="s">
         <v>7</v>
@@ -1334,36 +1334,36 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4">
-        <v>-459</v>
+        <v>-420</v>
       </c>
       <c r="C4">
-        <v>-514</v>
+        <v>-420</v>
       </c>
       <c r="D4">
-        <v>10.70038910505837</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>300</v>
+        <v>157</v>
       </c>
       <c r="F4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5">
-        <v>-497</v>
+        <v>-459</v>
       </c>
       <c r="C5">
-        <v>-623</v>
+        <v>-493</v>
       </c>
       <c r="D5">
-        <v>20.22471910112359</v>
+        <v>6.896551724137931</v>
       </c>
       <c r="E5">
         <v>300</v>
@@ -1374,16 +1374,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6">
-        <v>-507</v>
+        <v>-497</v>
       </c>
       <c r="C6">
-        <v>-623</v>
+        <v>-602</v>
       </c>
       <c r="D6">
-        <v>18.61958266452649</v>
+        <v>17.44186046511628</v>
       </c>
       <c r="E6">
         <v>300</v>
@@ -1394,16 +1394,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7">
-        <v>-547</v>
+        <v>-507</v>
       </c>
       <c r="C7">
         <v>-623</v>
       </c>
       <c r="D7">
-        <v>12.19903691813804</v>
+        <v>18.61958266452649</v>
       </c>
       <c r="E7">
         <v>300</v>
@@ -1414,16 +1414,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8">
-        <v>-562</v>
+        <v>-547</v>
       </c>
       <c r="C8">
         <v>-623</v>
       </c>
       <c r="D8">
-        <v>9.791332263242374</v>
+        <v>12.19903691813804</v>
       </c>
       <c r="E8">
         <v>300</v>
@@ -1434,16 +1434,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9">
-        <v>-596</v>
+        <v>-562</v>
       </c>
       <c r="C9">
         <v>-623</v>
       </c>
       <c r="D9">
-        <v>4.333868378812198</v>
+        <v>9.791332263242374</v>
       </c>
       <c r="E9">
         <v>300</v>
@@ -1454,16 +1454,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10">
-        <v>-603</v>
+        <v>-596</v>
       </c>
       <c r="C10">
         <v>-623</v>
       </c>
       <c r="D10">
-        <v>3.210272873194221</v>
+        <v>4.333868378812198</v>
       </c>
       <c r="E10">
         <v>300</v>
@@ -1474,16 +1474,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11">
-        <v>-613</v>
+        <v>-603</v>
       </c>
       <c r="C11">
         <v>-623</v>
       </c>
       <c r="D11">
-        <v>1.605136436597111</v>
+        <v>3.210272873194221</v>
       </c>
       <c r="E11">
         <v>300</v>
@@ -1494,27 +1494,27 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12">
-        <v>-623</v>
+        <v>-613</v>
       </c>
       <c r="C12">
         <v>-623</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>1.605136436597111</v>
       </c>
       <c r="E12">
-        <v>198</v>
+        <v>300</v>
       </c>
       <c r="F12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13">
         <v>-623</v>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>16</v>
+        <v>204</v>
       </c>
       <c r="F13" t="s">
         <v>7</v>
@@ -1534,7 +1534,7 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14">
         <v>-623</v>
@@ -1584,16 +1584,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2">
-        <v>-313</v>
+        <v>-359</v>
       </c>
       <c r="C2">
         <v>-1316</v>
       </c>
       <c r="D2">
-        <v>76.21580547112463</v>
+        <v>72.72036474164135</v>
       </c>
       <c r="E2">
         <v>300</v>
@@ -1604,16 +1604,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3">
-        <v>-383</v>
+        <v>-393</v>
       </c>
       <c r="C3">
         <v>-1316</v>
       </c>
       <c r="D3">
-        <v>70.8966565349544</v>
+        <v>70.13677811550151</v>
       </c>
       <c r="E3">
         <v>300</v>
@@ -1624,16 +1624,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4">
-        <v>-408</v>
+        <v>-420</v>
       </c>
       <c r="C4">
         <v>-1316</v>
       </c>
       <c r="D4">
-        <v>68.99696048632219</v>
+        <v>68.08510638297872</v>
       </c>
       <c r="E4">
         <v>300</v>
@@ -1644,16 +1644,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5">
-        <v>-421</v>
+        <v>-459</v>
       </c>
       <c r="C5">
         <v>-1316</v>
       </c>
       <c r="D5">
-        <v>68.00911854103343</v>
+        <v>65.12158054711246</v>
       </c>
       <c r="E5">
         <v>300</v>
@@ -1664,16 +1664,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6">
-        <v>-466</v>
+        <v>-497</v>
       </c>
       <c r="C6">
         <v>-1316</v>
       </c>
       <c r="D6">
-        <v>64.58966565349544</v>
+        <v>62.23404255319149</v>
       </c>
       <c r="E6">
         <v>300</v>
@@ -1684,16 +1684,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7">
-        <v>-492</v>
+        <v>-507</v>
       </c>
       <c r="C7">
         <v>-1316</v>
       </c>
       <c r="D7">
-        <v>62.61398176291794</v>
+        <v>61.4741641337386</v>
       </c>
       <c r="E7">
         <v>300</v>
@@ -1704,16 +1704,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8">
-        <v>-526</v>
+        <v>-547</v>
       </c>
       <c r="C8">
         <v>-1316</v>
       </c>
       <c r="D8">
-        <v>60.03039513677811</v>
+        <v>58.43465045592705</v>
       </c>
       <c r="E8">
         <v>300</v>
@@ -1724,16 +1724,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9">
-        <v>-519</v>
+        <v>-570</v>
       </c>
       <c r="C9">
         <v>-1316</v>
       </c>
       <c r="D9">
-        <v>60.56231003039514</v>
+        <v>56.6869300911854</v>
       </c>
       <c r="E9">
         <v>300</v>
@@ -1744,16 +1744,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10">
-        <v>-563</v>
+        <v>-596</v>
       </c>
       <c r="C10">
         <v>-1316</v>
       </c>
       <c r="D10">
-        <v>57.21884498480243</v>
+        <v>54.7112462006079</v>
       </c>
       <c r="E10">
         <v>300</v>
@@ -1764,16 +1764,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11">
-        <v>-570</v>
+        <v>-603</v>
       </c>
       <c r="C11">
         <v>-1316</v>
       </c>
       <c r="D11">
-        <v>56.6869300911854</v>
+        <v>54.17933130699089</v>
       </c>
       <c r="E11">
         <v>300</v>
@@ -1784,16 +1784,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12">
-        <v>-584</v>
+        <v>-613</v>
       </c>
       <c r="C12">
         <v>-1316</v>
       </c>
       <c r="D12">
-        <v>55.62310030395137</v>
+        <v>53.419452887538</v>
       </c>
       <c r="E12">
         <v>300</v>
@@ -1804,16 +1804,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13">
-        <v>-613</v>
+        <v>-623</v>
       </c>
       <c r="C13">
         <v>-1316</v>
       </c>
       <c r="D13">
-        <v>53.419452887538</v>
+        <v>52.6595744680851</v>
       </c>
       <c r="E13">
         <v>300</v>
@@ -1824,16 +1824,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14">
-        <v>-562</v>
+        <v>-623</v>
       </c>
       <c r="C14">
         <v>-1316</v>
       </c>
       <c r="D14">
-        <v>57.29483282674772</v>
+        <v>52.6595744680851</v>
       </c>
       <c r="E14">
         <v>300</v>

--- a/hexaly_benchmarking_results/original_2.xlsx
+++ b/hexaly_benchmarking_results/original_2.xlsx
@@ -746,7 +746,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F3" t="s">
         <v>7</v>
@@ -946,7 +946,7 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="F13" t="s">
         <v>7</v>
@@ -966,7 +966,7 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F14" t="s">
         <v>7</v>
@@ -1326,7 +1326,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F3" t="s">
         <v>7</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F4" t="s">
         <v>7</v>
@@ -1360,10 +1360,10 @@
         <v>-459</v>
       </c>
       <c r="C5">
-        <v>-493</v>
+        <v>-483</v>
       </c>
       <c r="D5">
-        <v>6.896551724137931</v>
+        <v>4.968944099378882</v>
       </c>
       <c r="E5">
         <v>300</v>
@@ -1380,10 +1380,10 @@
         <v>-497</v>
       </c>
       <c r="C6">
-        <v>-602</v>
+        <v>-589</v>
       </c>
       <c r="D6">
-        <v>17.44186046511628</v>
+        <v>15.61969439728353</v>
       </c>
       <c r="E6">
         <v>300</v>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>204</v>
+        <v>293</v>
       </c>
       <c r="F13" t="s">
         <v>7</v>
@@ -1546,7 +1546,7 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F14" t="s">
         <v>7</v>
